--- a/public/TagWarningLuyenCoc.xlsx
+++ b/public/TagWarningLuyenCoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AFB962-10C3-479E-AC86-120DD0145EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E2277B-C8C6-47D7-9FEC-768664C69D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" firstSheet="4" activeTab="6" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="LocBuiMoiTruongMatDat1" sheetId="28" r:id="rId1"/>
@@ -33,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="331">
   <si>
     <t>Nhiệt độ trước bộ giảm nhiệt A (°C)</t>
   </si>
@@ -95,9 +93,6 @@
     <t>LB_PHANTRAM</t>
   </si>
   <si>
-    <t>Dòng điện động cơ QLB (A)</t>
-  </si>
-  <si>
     <t>Tag5</t>
   </si>
   <si>
@@ -107,9 +102,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>Độ rung gối đỡ trước QLB  (mm/s)</t>
-  </si>
-  <si>
     <t>Tag6</t>
   </si>
   <si>
@@ -119,18 +111,12 @@
     <t>mm/s</t>
   </si>
   <si>
-    <t>Độ rung gối đỡ sau QLB  (mm/s)</t>
-  </si>
-  <si>
     <t>Tag7</t>
   </si>
   <si>
     <t>LB_RUNGGOISAU</t>
   </si>
   <si>
-    <t>Nhiệt độ gối đỡ trước QLB（℃）</t>
-  </si>
-  <si>
     <t>Tag8</t>
   </si>
   <si>
@@ -140,54 +126,36 @@
     <t>℃</t>
   </si>
   <si>
-    <t>Nhiệt độ gối đỡ sau QLB (℃）</t>
-  </si>
-  <si>
     <t>Tag9</t>
   </si>
   <si>
     <t>LB_NDGOISAU</t>
   </si>
   <si>
-    <t>Nhiệt độ vòng bi trước  QLB (℃）</t>
-  </si>
-  <si>
     <t>Tag10</t>
   </si>
   <si>
     <t>LB_NDBITRC</t>
   </si>
   <si>
-    <t>Nhiệt độ vòng bi sau QLB（℃）</t>
-  </si>
-  <si>
     <t>Tag11</t>
   </si>
   <si>
     <t>LB_NDBISAU</t>
   </si>
   <si>
-    <t>Nhiệt độ cuộn dây U QLB （℃）</t>
-  </si>
-  <si>
     <t>Tag12</t>
   </si>
   <si>
     <t>LB_U</t>
   </si>
   <si>
-    <t>Nhiệt độ cuộn dây V QLB （℃）</t>
-  </si>
-  <si>
     <t>Tag13</t>
   </si>
   <si>
     <t>LB_V</t>
   </si>
   <si>
-    <t>Nhiệt độ cuộn dây W QLB（℃）</t>
-  </si>
-  <si>
     <t>Tag14</t>
   </si>
   <si>
@@ -200,15 +168,6 @@
     <t>Ngưỡng Nguy Hiểm</t>
   </si>
   <si>
-    <t>TE_14601A</t>
-  </si>
-  <si>
-    <t>TE_14601B</t>
-  </si>
-  <si>
-    <t>TE_14602</t>
-  </si>
-  <si>
     <t>LB2_TOCDOQUAT</t>
   </si>
   <si>
@@ -248,57 +207,30 @@
     <t>Quạt tuần hoàn</t>
   </si>
   <si>
-    <t>Độ rung  gối đỡ trước 2VT-14101A (mm/s)</t>
-  </si>
-  <si>
     <t>QGTH1_RUNGGOITRUOC</t>
   </si>
   <si>
-    <t>Độ rung  gối đỡ sau 2VT-14102A (mm/s)</t>
-  </si>
-  <si>
     <t>QGTH1_RUNGGOISAU</t>
   </si>
   <si>
-    <t>Nhiệt độ gối đỡ trước 2TE-14114A（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_NDGOIDOTRC</t>
   </si>
   <si>
-    <t>Nhiệt độ gối đỡ sau 2TE-14114B（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_NDGOIDOSAU</t>
   </si>
   <si>
-    <t>Nhiệt độ vòng bi trước 2TE-14115A（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_NDVBTRC</t>
   </si>
   <si>
-    <t>Nhiệt độ vòng bi sau 2TE-14115B（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_NDVBSAU</t>
   </si>
   <si>
-    <t xml:space="preserve"> Nhiệt độ cuộn dây U 2TE-14113A（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_U</t>
   </si>
   <si>
-    <t>Nhiệt độ cuộn dây V 2TE-14113B（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_V</t>
   </si>
   <si>
-    <t>Nhiệt độ cuộn dây W 2TE-14113C（℃）</t>
-  </si>
-  <si>
     <t>QGTH1_W</t>
   </si>
   <si>
@@ -314,24 +246,15 @@
     <t>QGTH1_DONGDIEN</t>
   </si>
   <si>
-    <t>Nhiệt độ thiết bị đo mức radar 2TT-14118（℃）</t>
-  </si>
-  <si>
     <t>CDQ1_NDRADAR</t>
   </si>
   <si>
-    <t>Áp suất khí nito cấp vào thiết bị đo mức điện dung LBL1 PIA-14110 (KPa)</t>
-  </si>
-  <si>
     <t>CDQ1_NITOLB1</t>
   </si>
   <si>
     <t>Kpa</t>
   </si>
   <si>
-    <t>Áp suất khí nito cấp vào thiết bị đo mức điện dung LBL2 PIA-14111(KPa)</t>
-  </si>
-  <si>
     <t>CDQ1_NITOLB2</t>
   </si>
   <si>
@@ -1041,6 +964,75 @@
   </si>
   <si>
     <t>NhietDoVongBi2_PV</t>
+  </si>
+  <si>
+    <t>TE_14601</t>
+  </si>
+  <si>
+    <t>TE_14603</t>
+  </si>
+  <si>
+    <t>TE_14604</t>
+  </si>
+  <si>
+    <t>Dòng điện làm việc (A)</t>
+  </si>
+  <si>
+    <t>Độ rung gối đỡ trước   (mm/s)</t>
+  </si>
+  <si>
+    <t>Độ rung gối đỡ sau  (mm/s)</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối đỡ trước（℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối đỡ sau (℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ vòng bi trước động cơ  (℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ vòng bi sau động cơ（℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây U（℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây V （℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây W（℃）</t>
+  </si>
+  <si>
+    <t>Độ rung  gối đỡ trước (mm/s)</t>
+  </si>
+  <si>
+    <t>Độ rung  gối đỡ sau (mm/s)</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối đỡ trước （℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối đỡ sau （℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ vòng bi trước （℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ vòng bi sau（℃）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhiệt độ cuộn dây U （℃）</t>
+  </si>
+  <si>
+    <t>Nhiệt độ thiết bị đo mức radar （℃）</t>
+  </si>
+  <si>
+    <t>Áp suất khí nito cấp vào thiết bị đo mức điện dung LBL1 (KPa)</t>
+  </si>
+  <si>
+    <t>Áp suất khí nito cấp vào thiết bị đo mức điện dung LBL2 (KPa)</t>
   </si>
 </sst>
 </file>
@@ -1300,14 +1292,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1664,10 +1656,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1685,10 +1677,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1706,10 +1698,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1767,18 +1759,18 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="F6" s="10">
         <v>80</v>
@@ -1788,18 +1780,18 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="10">
         <v>6</v>
@@ -1809,18 +1801,18 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="22"/>
+      <c r="A8" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="10">
         <v>6</v>
@@ -1830,18 +1822,18 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="22"/>
+      <c r="A9" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="21"/>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="10">
         <v>75</v>
@@ -1851,18 +1843,18 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="20"/>
+      <c r="A10" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="22"/>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10" s="10">
         <v>75</v>
@@ -1872,18 +1864,18 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="22"/>
+      <c r="A11" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="10">
         <v>85</v>
@@ -1893,18 +1885,18 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="22"/>
+      <c r="A12" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="10">
         <v>85</v>
@@ -1914,18 +1906,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="22"/>
+      <c r="A13" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F13" s="10">
         <v>145</v>
@@ -1935,18 +1927,18 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="22"/>
+      <c r="A14" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F14" s="10">
         <v>145</v>
@@ -1956,18 +1948,18 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="22"/>
+      <c r="A15" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F15" s="10">
         <v>145</v>
@@ -1978,19 +1970,14 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F16" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -2000,6 +1987,11 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2020,15 +2012,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>308</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2041,15 +2033,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>309</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -2062,15 +2054,15 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>310</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -2093,7 +2085,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
@@ -2114,7 +2106,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>14</v>
@@ -2123,18 +2115,18 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="14">
         <v>65</v>
@@ -2144,18 +2136,18 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="22"/>
+      <c r="A7" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="14">
         <v>6.5</v>
@@ -2165,18 +2157,18 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="22"/>
+      <c r="A8" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="14">
         <v>6.5</v>
@@ -2186,18 +2178,18 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="22"/>
+      <c r="A9" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="21"/>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="14">
         <v>70</v>
@@ -2207,18 +2199,18 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="20"/>
+      <c r="A10" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="22"/>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10" s="14">
         <v>70</v>
@@ -2228,18 +2220,18 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="22"/>
+      <c r="A11" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="14">
         <v>90</v>
@@ -2249,18 +2241,18 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="22"/>
+      <c r="A12" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="14">
         <v>90</v>
@@ -2270,18 +2262,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="22"/>
+      <c r="A13" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F13" s="14">
         <v>150</v>
@@ -2291,18 +2283,18 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="22"/>
+      <c r="A14" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F14" s="14">
         <v>150</v>
@@ -2312,18 +2304,18 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="22"/>
+      <c r="A15" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F15" s="14">
         <v>150</v>
@@ -2334,19 +2326,14 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F16" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -2356,6 +2343,11 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2377,19 +2369,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F1" s="16">
         <v>6.3</v>
@@ -2401,16 +2393,16 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26"/>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="18">
         <v>6.3</v>
@@ -2422,16 +2414,16 @@
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="18">
         <v>80</v>
@@ -2443,16 +2435,16 @@
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="18">
         <v>80</v>
@@ -2464,16 +2456,16 @@
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26"/>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="18">
         <v>90</v>
@@ -2485,16 +2477,16 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26"/>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="18">
         <v>90</v>
@@ -2506,16 +2498,16 @@
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26"/>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="18">
         <v>140</v>
@@ -2527,16 +2519,16 @@
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26"/>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="18">
         <v>140</v>
@@ -2548,16 +2540,16 @@
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="18">
         <v>140</v>
@@ -2569,13 +2561,13 @@
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
@@ -2590,16 +2582,16 @@
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27"/>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="18">
         <v>70</v>
@@ -2611,16 +2603,16 @@
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="18">
         <v>50</v>
@@ -2632,16 +2624,16 @@
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="3" t="s">
-        <v>92</v>
+        <v>329</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F13" s="18">
         <v>25</v>
@@ -2653,16 +2645,16 @@
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F14" s="18">
         <v>25</v>
@@ -2673,10 +2665,10 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2703,19 +2695,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F1" s="16">
         <v>6.3</v>
@@ -2727,16 +2719,16 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="18">
         <v>6.3</v>
@@ -2748,16 +2740,16 @@
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="18">
         <v>80</v>
@@ -2769,16 +2761,16 @@
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="18">
         <v>80</v>
@@ -2790,16 +2782,16 @@
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28"/>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="18">
         <v>90</v>
@@ -2811,16 +2803,16 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28"/>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="18">
         <v>90</v>
@@ -2832,16 +2824,16 @@
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="18">
         <v>140</v>
@@ -2853,16 +2845,16 @@
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="18">
         <v>140</v>
@@ -2874,16 +2866,16 @@
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="18">
         <v>140</v>
@@ -2895,13 +2887,13 @@
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
@@ -2916,16 +2908,16 @@
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="18">
         <v>70</v>
@@ -2936,19 +2928,19 @@
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="18">
         <v>50</v>
@@ -2960,16 +2952,16 @@
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="3" t="s">
-        <v>92</v>
+        <v>329</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F13" s="18">
         <v>25</v>
@@ -2981,16 +2973,16 @@
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F14" s="18">
         <v>25</v>
@@ -3001,10 +2993,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3031,19 +3023,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F1" s="16">
         <v>6.3</v>
@@ -3055,16 +3047,16 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="18">
         <v>6.3</v>
@@ -3076,16 +3068,16 @@
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="18">
         <v>75</v>
@@ -3097,16 +3089,16 @@
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="18">
         <v>75</v>
@@ -3118,16 +3110,16 @@
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28"/>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="18">
         <v>95</v>
@@ -3139,16 +3131,16 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28"/>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="18">
         <v>95</v>
@@ -3160,16 +3152,16 @@
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="18">
         <v>130</v>
@@ -3181,16 +3173,16 @@
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="18">
         <v>130</v>
@@ -3202,16 +3194,16 @@
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="18">
         <v>130</v>
@@ -3223,13 +3215,13 @@
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
@@ -3244,16 +3236,16 @@
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="18">
         <v>50</v>
@@ -3264,19 +3256,19 @@
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="18">
         <v>50</v>
@@ -3288,16 +3280,16 @@
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
       <c r="B13" s="3" t="s">
-        <v>92</v>
+        <v>329</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F13" s="18">
         <v>25</v>
@@ -3309,16 +3301,16 @@
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F14" s="18">
         <v>25</v>
@@ -3329,10 +3321,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3359,19 +3351,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F1" s="12">
         <v>70</v>
@@ -3383,16 +3375,16 @@
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="30"/>
       <c r="B2" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F2" s="14">
         <v>70</v>
@@ -3404,16 +3396,16 @@
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="30"/>
       <c r="B3" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="14">
         <v>100</v>
@@ -3425,16 +3417,16 @@
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="30"/>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="14">
         <v>100</v>
@@ -3446,16 +3438,16 @@
     <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="30"/>
       <c r="B5" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="14">
         <v>100</v>
@@ -3467,16 +3459,16 @@
     <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="30"/>
       <c r="B6" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="14">
         <v>90</v>
@@ -3488,16 +3480,16 @@
     <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="30"/>
       <c r="B7" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="14">
         <v>90</v>
@@ -3509,16 +3501,16 @@
     <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="30"/>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="14">
         <v>60</v>
@@ -3530,16 +3522,16 @@
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="30"/>
       <c r="B9" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="14">
         <v>3.5</v>
@@ -3551,16 +3543,16 @@
     <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" s="14">
         <v>3.5</v>
@@ -3571,19 +3563,19 @@
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="14">
         <v>70</v>
@@ -3595,16 +3587,16 @@
     <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F12" s="14">
         <v>70</v>
@@ -3616,16 +3608,16 @@
     <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F13" s="14">
         <v>100</v>
@@ -3637,16 +3629,16 @@
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="30"/>
       <c r="B14" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F14" s="14">
         <v>100</v>
@@ -3658,16 +3650,16 @@
     <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="30"/>
       <c r="B15" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F15" s="14">
         <v>100</v>
@@ -3679,16 +3671,16 @@
     <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="30"/>
       <c r="B16" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F16" s="14">
         <v>90</v>
@@ -3700,16 +3692,16 @@
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="30"/>
       <c r="B17" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F17" s="14">
         <v>90</v>
@@ -3721,16 +3713,16 @@
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
       <c r="B18" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="14">
         <v>60</v>
@@ -3742,16 +3734,16 @@
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="30"/>
       <c r="B19" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F19" s="14">
         <v>3.5</v>
@@ -3763,16 +3755,16 @@
     <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="30"/>
       <c r="B20" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F20" s="14">
         <v>3.5</v>
@@ -3783,19 +3775,19 @@
     </row>
     <row r="21" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F21" s="14">
         <v>70</v>
@@ -3807,16 +3799,16 @@
     <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="30"/>
       <c r="B22" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22" s="14">
         <v>70</v>
@@ -3828,16 +3820,16 @@
     <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="30"/>
       <c r="B23" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F23" s="14">
         <v>100</v>
@@ -3849,16 +3841,16 @@
     <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="30"/>
       <c r="B24" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F24" s="14">
         <v>100</v>
@@ -3870,16 +3862,16 @@
     <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="30"/>
       <c r="B25" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F25" s="14">
         <v>100</v>
@@ -3891,16 +3883,16 @@
     <row r="26" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="30"/>
       <c r="B26" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F26" s="14">
         <v>90</v>
@@ -3912,16 +3904,16 @@
     <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="30"/>
       <c r="B27" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F27" s="14">
         <v>90</v>
@@ -3933,16 +3925,16 @@
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
       <c r="B28" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" s="14">
         <v>60</v>
@@ -3954,16 +3946,16 @@
     <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="30"/>
       <c r="B29" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
         <v>6.3</v>
@@ -3975,16 +3967,16 @@
     <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="30"/>
       <c r="B30" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F30" s="14">
         <v>6.3</v>
@@ -3995,19 +3987,19 @@
     </row>
     <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F31" s="14">
         <v>70</v>
@@ -4019,16 +4011,16 @@
     <row r="32" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="30"/>
       <c r="B32" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F32" s="14">
         <v>70</v>
@@ -4040,16 +4032,16 @@
     <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="30"/>
       <c r="B33" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F33" s="14">
         <v>100</v>
@@ -4061,16 +4053,16 @@
     <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="30"/>
       <c r="B34" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F34" s="14">
         <v>100</v>
@@ -4082,16 +4074,16 @@
     <row r="35" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="30"/>
       <c r="B35" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F35" s="14">
         <v>100</v>
@@ -4103,16 +4095,16 @@
     <row r="36" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="30"/>
       <c r="B36" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F36" s="14">
         <v>90</v>
@@ -4124,16 +4116,16 @@
     <row r="37" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="30"/>
       <c r="B37" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F37" s="14">
         <v>90</v>
@@ -4145,16 +4137,16 @@
     <row r="38" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="30"/>
       <c r="B38" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38" s="14">
         <v>60</v>
@@ -4166,16 +4158,16 @@
     <row r="39" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="30"/>
       <c r="B39" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F39" s="14">
         <v>3.5</v>
@@ -4187,16 +4179,16 @@
     <row r="40" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="30"/>
       <c r="B40" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F40" s="14">
         <v>3.5</v>
@@ -4207,19 +4199,19 @@
     </row>
     <row r="41" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F41" s="14">
         <v>70</v>
@@ -4231,16 +4223,16 @@
     <row r="42" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="30"/>
       <c r="B42" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F42" s="14">
         <v>70</v>
@@ -4252,16 +4244,16 @@
     <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="30"/>
       <c r="B43" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F43" s="14">
         <v>100</v>
@@ -4273,16 +4265,16 @@
     <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="30"/>
       <c r="B44" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F44" s="14">
         <v>100</v>
@@ -4294,16 +4286,16 @@
     <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="30"/>
       <c r="B45" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F45" s="14">
         <v>100</v>
@@ -4315,16 +4307,16 @@
     <row r="46" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="30"/>
       <c r="B46" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F46" s="14">
         <v>90</v>
@@ -4336,16 +4328,16 @@
     <row r="47" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="30"/>
       <c r="B47" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F47" s="14">
         <v>90</v>
@@ -4357,16 +4349,16 @@
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
       <c r="B48" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F48" s="14">
         <v>60</v>
@@ -4378,16 +4370,16 @@
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="30"/>
       <c r="B49" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F49" s="14">
         <v>3.5</v>
@@ -4399,16 +4391,16 @@
     <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="30"/>
       <c r="B50" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F50" s="14">
         <v>3.5</v>
@@ -4419,19 +4411,19 @@
     </row>
     <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F51" s="14">
         <v>70</v>
@@ -4443,16 +4435,16 @@
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="30"/>
       <c r="B52" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F52" s="14">
         <v>70</v>
@@ -4464,16 +4456,16 @@
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="30"/>
       <c r="B53" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F53" s="14">
         <v>100</v>
@@ -4485,16 +4477,16 @@
     <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="30"/>
       <c r="B54" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F54" s="14">
         <v>100</v>
@@ -4506,16 +4498,16 @@
     <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="30"/>
       <c r="B55" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F55" s="14">
         <v>100</v>
@@ -4527,16 +4519,16 @@
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="30"/>
       <c r="B56" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F56" s="14">
         <v>90</v>
@@ -4548,16 +4540,16 @@
     <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A57" s="30"/>
       <c r="B57" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F57" s="14">
         <v>90</v>
@@ -4569,16 +4561,16 @@
     <row r="58" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A58" s="30"/>
       <c r="B58" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F58" s="14">
         <v>60</v>
@@ -4590,16 +4582,16 @@
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="30"/>
       <c r="B59" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F59" s="14">
         <v>6.3</v>
@@ -4611,16 +4603,16 @@
     <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="30"/>
       <c r="B60" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F60" s="14">
         <v>6.3</v>
@@ -4631,19 +4623,19 @@
     </row>
     <row r="61" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F61" s="14">
         <v>70</v>
@@ -4655,16 +4647,16 @@
     <row r="62" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="30"/>
       <c r="B62" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F62" s="14">
         <v>70</v>
@@ -4676,16 +4668,16 @@
     <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A63" s="30"/>
       <c r="B63" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F63" s="14">
         <v>100</v>
@@ -4697,16 +4689,16 @@
     <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A64" s="30"/>
       <c r="B64" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F64" s="14">
         <v>100</v>
@@ -4718,16 +4710,16 @@
     <row r="65" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="30"/>
       <c r="B65" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F65" s="14">
         <v>100</v>
@@ -4739,16 +4731,16 @@
     <row r="66" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="30"/>
       <c r="B66" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F66" s="14">
         <v>90</v>
@@ -4760,16 +4752,16 @@
     <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A67" s="30"/>
       <c r="B67" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F67" s="14">
         <v>90</v>
@@ -4781,16 +4773,16 @@
     <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="30"/>
       <c r="B68" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F68" s="14">
         <v>60</v>
@@ -4802,16 +4794,16 @@
     <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A69" s="30"/>
       <c r="B69" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F69" s="14">
         <v>6.3</v>
@@ -4823,16 +4815,16 @@
     <row r="70" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A70" s="30"/>
       <c r="B70" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F70" s="14">
         <v>6.3</v>
@@ -4843,19 +4835,19 @@
     </row>
     <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A71" s="29" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F71" s="14">
         <v>70</v>
@@ -4867,16 +4859,16 @@
     <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A72" s="30"/>
       <c r="B72" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F72" s="14">
         <v>70</v>
@@ -4888,16 +4880,16 @@
     <row r="73" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="30"/>
       <c r="B73" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F73" s="14">
         <v>100</v>
@@ -4909,16 +4901,16 @@
     <row r="74" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A74" s="30"/>
       <c r="B74" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F74" s="14">
         <v>100</v>
@@ -4930,16 +4922,16 @@
     <row r="75" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="30"/>
       <c r="B75" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F75" s="14">
         <v>100</v>
@@ -4951,16 +4943,16 @@
     <row r="76" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A76" s="30"/>
       <c r="B76" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F76" s="14">
         <v>90</v>
@@ -4972,16 +4964,16 @@
     <row r="77" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A77" s="30"/>
       <c r="B77" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F77" s="14">
         <v>90</v>
@@ -4993,16 +4985,16 @@
     <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A78" s="30"/>
       <c r="B78" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F78" s="14">
         <v>60</v>
@@ -5014,16 +5006,16 @@
     <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A79" s="30"/>
       <c r="B79" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F79" s="14">
         <v>6.3</v>
@@ -5035,16 +5027,16 @@
     <row r="80" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A80" s="30"/>
       <c r="B80" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F80" s="14">
         <v>6.3</v>
@@ -5055,19 +5047,19 @@
     </row>
     <row r="81" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A81" s="29" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F81" s="14">
         <v>70</v>
@@ -5079,16 +5071,16 @@
     <row r="82" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A82" s="30"/>
       <c r="B82" s="4" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F82" s="14">
         <v>70</v>
@@ -5100,16 +5092,16 @@
     <row r="83" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A83" s="30"/>
       <c r="B83" s="4" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F83" s="14">
         <v>100</v>
@@ -5121,16 +5113,16 @@
     <row r="84" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A84" s="30"/>
       <c r="B84" s="4" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F84" s="14">
         <v>100</v>
@@ -5142,16 +5134,16 @@
     <row r="85" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A85" s="30"/>
       <c r="B85" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F85" s="14">
         <v>100</v>
@@ -5163,16 +5155,16 @@
     <row r="86" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A86" s="30"/>
       <c r="B86" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F86" s="14">
         <v>90</v>
@@ -5184,16 +5176,16 @@
     <row r="87" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A87" s="30"/>
       <c r="B87" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F87" s="14">
         <v>90</v>
@@ -5205,16 +5197,16 @@
     <row r="88" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A88" s="30"/>
       <c r="B88" s="4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F88" s="14">
         <v>60</v>
@@ -5226,16 +5218,16 @@
     <row r="89" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A89" s="30"/>
       <c r="B89" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F89" s="14">
         <v>6.3</v>
@@ -5247,16 +5239,16 @@
     <row r="90" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A90" s="31"/>
       <c r="B90" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F90" s="14">
         <v>6.3</v>
@@ -5267,10 +5259,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F91" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -5306,85 +5298,85 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6">
         <v>135</v>
@@ -5395,17 +5387,17 @@
     </row>
     <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B6" s="32"/>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="6">
         <v>135</v>
@@ -5416,17 +5408,17 @@
     </row>
     <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="6">
         <v>135</v>
@@ -5437,17 +5429,17 @@
     </row>
     <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="6">
@@ -5456,17 +5448,17 @@
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6">
@@ -5475,17 +5467,17 @@
     </row>
     <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="6">
@@ -5494,17 +5486,17 @@
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="6">
@@ -5513,25 +5505,25 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F12" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
